--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachanon.K\AppData\Roaming\eq_aa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachanon.K\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083B657B-8D8D-45EB-8339-CF68476AEB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9CE831-7DAE-44A4-B04D-0FDCF7C164FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,10 +537,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>EQPTZ2501093</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>EFAZZ0001605</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -670,13 +666,6 @@
   </si>
   <si>
     <t>400G PSM4     #05</t>
-  </si>
-  <si>
-    <t>EZDYH2400195</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>400G PSM4     #07</t>
   </si>
   <si>
     <t>EFAZZ0001603</t>
@@ -1213,10 +1202,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>800G PSM8    #12</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>800G DR8 AWS #01</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1420,9 +1405,6 @@
     <t>800G DR8     #13</t>
   </si>
   <si>
-    <t xml:space="preserve">TX AA </t>
-  </si>
-  <si>
     <t>EZDYH2400080</t>
   </si>
   <si>
@@ -1432,9 +1414,6 @@
     <t>800G PSM8    #10</t>
   </si>
   <si>
-    <t>800G PSM8    #11</t>
-  </si>
-  <si>
     <t>EZDYH2400054</t>
   </si>
   <si>
@@ -1453,19 +1432,37 @@
     <t>800G 2XFR4  OUT  #06</t>
   </si>
   <si>
-    <t>800G 2XFR4  OUT  #07</t>
-  </si>
-  <si>
     <t>EQPTZ2501067</t>
   </si>
   <si>
     <t>EQPTZ2500009</t>
   </si>
   <si>
-    <t>800G 2XFR4    #13</t>
-  </si>
-  <si>
     <t>800G 2XFR4    #10</t>
+  </si>
+  <si>
+    <t>EQPTZ2501093</t>
+  </si>
+  <si>
+    <t>800G 2XFR4    #09</t>
+  </si>
+  <si>
+    <t>EZDYH2400195</t>
+  </si>
+  <si>
+    <t>800G 2XFR4  OUT  #05</t>
+  </si>
+  <si>
+    <t>400G DR4       #01</t>
+  </si>
+  <si>
+    <t>400G DR4       #02</t>
+  </si>
+  <si>
+    <t>800G DR8     #14</t>
+  </si>
+  <si>
+    <t>1.6T  DR8   NPI</t>
   </si>
 </sst>
 </file>
@@ -1867,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C247"/>
+  <dimension ref="A1:C250"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.08984375" customWidth="1"/>
@@ -1899,7 +1896,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -2585,10 +2582,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>88</v>
@@ -2596,10 +2593,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>88</v>
@@ -2607,10 +2604,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>88</v>
@@ -2618,10 +2615,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>88</v>
@@ -2629,10 +2626,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>88</v>
@@ -2640,59 +2637,53 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="C72" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="1"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
+      <c r="A73" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>324</v>
+        <v>304</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>401</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A75" s="1"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A76" s="1"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>154</v>
+        <v>273</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>2</v>
@@ -2700,10 +2691,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>2</v>
@@ -2711,10 +2702,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>2</v>
@@ -2722,10 +2713,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>2</v>
@@ -2733,10 +2724,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>2</v>
@@ -2744,21 +2735,21 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="1" t="s">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>325</v>
+        <v>157</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>242</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="1" t="s">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>336</v>
+        <v>159</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>2</v>
@@ -2766,10 +2757,10 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="1" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>337</v>
+        <v>161</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>2</v>
@@ -2777,75 +2768,75 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
-        <v>338</v>
+        <v>234</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="1" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>370</v>
+        <v>332</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="1"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
+      <c r="A87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="1"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
+      <c r="A88" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="1" t="s">
-        <v>163</v>
+        <v>365</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A90" s="1"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A91" s="1"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>88</v>
@@ -2853,10 +2844,10 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>88</v>
@@ -2864,10 +2855,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>88</v>
@@ -2875,10 +2866,10 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>88</v>
@@ -2886,10 +2877,10 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>88</v>
@@ -2897,10 +2888,10 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>88</v>
@@ -2908,10 +2899,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>88</v>
@@ -2919,10 +2910,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1" t="s">
-        <v>350</v>
+        <v>176</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>351</v>
+        <v>177</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>88</v>
@@ -2930,48 +2921,48 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1" t="s">
-        <v>352</v>
+        <v>178</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>353</v>
+        <v>179</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="1"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
+      <c r="A101" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="1" t="s">
-        <v>183</v>
+        <v>348</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>184</v>
+        <v>349</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A103" s="1"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>88</v>
@@ -2979,10 +2970,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>88</v>
@@ -2990,10 +2981,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>88</v>
@@ -3001,10 +2992,10 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>88</v>
@@ -3012,10 +3003,10 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>88</v>
@@ -3023,10 +3014,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>88</v>
@@ -3034,10 +3025,10 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>88</v>
@@ -3045,10 +3036,10 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="1" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>88</v>
@@ -3056,10 +3047,10 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>88</v>
@@ -3067,10 +3058,10 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>88</v>
@@ -3078,10 +3069,10 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="1" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>88</v>
@@ -3089,10 +3080,10 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>88</v>
@@ -3100,10 +3091,10 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>88</v>
@@ -3111,10 +3102,10 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>88</v>
@@ -3122,10 +3113,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>88</v>
@@ -3133,10 +3124,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>88</v>
@@ -3144,10 +3135,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>88</v>
@@ -3155,10 +3146,10 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>88</v>
@@ -3166,48 +3157,48 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="1"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
+      <c r="A123" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A125" s="1"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>88</v>
@@ -3215,10 +3206,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>88</v>
@@ -3226,135 +3217,135 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="1" t="s">
-        <v>354</v>
+        <v>226</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>355</v>
+        <v>227</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="1"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
+      <c r="A129" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
-        <v>233</v>
+        <v>350</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>234</v>
+        <v>351</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>242</v>
+        <v>88</v>
       </c>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>242</v>
-      </c>
+      <c r="A131" s="1"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
-        <v>335</v>
+        <v>237</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>334</v>
+        <v>238</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="1" t="s">
-        <v>393</v>
+        <v>235</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>394</v>
+        <v>236</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="1" t="s">
-        <v>395</v>
+        <v>331</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>396</v>
+        <v>330</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="1"/>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
+      <c r="A137" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="1"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
+      <c r="A138" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A139" s="1"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A140" s="1"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>88</v>
@@ -3362,10 +3353,10 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>88</v>
@@ -3373,10 +3364,10 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>88</v>
@@ -3384,10 +3375,10 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>88</v>
@@ -3395,10 +3386,10 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>88</v>
@@ -3406,10 +3397,10 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>88</v>
@@ -3417,10 +3408,10 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="1" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>88</v>
@@ -3428,10 +3419,10 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="1" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>333</v>
+        <v>255</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>88</v>
@@ -3439,10 +3430,10 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="1" t="s">
-        <v>400</v>
+        <v>147</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>402</v>
+        <v>327</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>88</v>
@@ -3450,143 +3441,149 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
-        <v>401</v>
+        <v>146</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>403</v>
+        <v>329</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="151" spans="1:3">
-      <c r="A151" s="1"/>
-      <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
+      <c r="A151" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="152" spans="1:3">
-      <c r="A152" s="1"/>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
+      <c r="A152" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>261</v>
-      </c>
+      <c r="A153" s="1"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>261</v>
-      </c>
+      <c r="A154" s="1"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="1" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="1" t="s">
-        <v>397</v>
+        <v>261</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>398</v>
+        <v>262</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" s="1"/>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" s="1"/>
-      <c r="B160" s="2"/>
-      <c r="C160" s="2"/>
+      <c r="C160" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="1" t="s">
+      <c r="A161" s="1"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="1"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163" s="1"/>
-      <c r="B163" s="2"/>
-      <c r="C163" s="2"/>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="1"/>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
+      <c r="C164" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>242</v>
-      </c>
+      <c r="A165" s="1"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1"/>
@@ -3594,20 +3591,20 @@
       <c r="C166" s="2"/>
     </row>
     <row r="167" spans="1:3">
-      <c r="A167" s="1"/>
-      <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
+      <c r="A167" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="168" spans="1:3">
-      <c r="A168" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>261</v>
-      </c>
+      <c r="A168" s="1"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="1"/>
@@ -3615,9 +3612,15 @@
       <c r="C169" s="2"/>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="1"/>
-      <c r="B170" s="2"/>
-      <c r="C170" s="2"/>
+      <c r="A170" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="1"/>
@@ -3626,72 +3629,66 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="1"/>
-      <c r="B172" s="4"/>
+      <c r="B172" s="2"/>
       <c r="C172" s="2"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A173" s="1"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1"/>
-      <c r="B174" s="2"/>
+      <c r="B174" s="4"/>
       <c r="C174" s="2"/>
     </row>
     <row r="175" spans="1:3">
-      <c r="A175" s="1"/>
-      <c r="B175" s="2"/>
-      <c r="C175" s="2"/>
+      <c r="A175" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="176" spans="1:3">
-      <c r="A176" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A176" s="1"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A177" s="1"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="1"/>
-      <c r="B178" s="2"/>
-      <c r="C178" s="2"/>
+      <c r="A178" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="179" spans="1:3">
-      <c r="A179" s="1"/>
-      <c r="B179" s="2"/>
-      <c r="C179" s="2"/>
+      <c r="A179" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A180" s="1"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="1"/>
@@ -3699,9 +3696,15 @@
       <c r="C181" s="2"/>
     </row>
     <row r="182" spans="1:3">
-      <c r="A182" s="1"/>
-      <c r="B182" s="2"/>
-      <c r="C182" s="2"/>
+      <c r="A182" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="1"/>
@@ -3714,33 +3717,21 @@
       <c r="C184" s="2"/>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A185" s="1"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A186" s="1"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>2</v>
@@ -3748,10 +3739,10 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="7" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>2</v>
@@ -3759,10 +3750,10 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>2</v>
@@ -3770,10 +3761,10 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="7" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>2</v>
@@ -3781,10 +3772,10 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>2</v>
@@ -3792,21 +3783,21 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="7" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="1" t="s">
-        <v>9</v>
+      <c r="A193" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>332</v>
+        <v>294</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>2</v>
@@ -3814,10 +3805,10 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="1" t="s">
-        <v>389</v>
+        <v>9</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>2</v>
@@ -3825,10 +3816,10 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>2</v>
@@ -3851,10 +3842,10 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>88</v>
@@ -3862,10 +3853,10 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>88</v>
@@ -3873,10 +3864,10 @@
     </row>
     <row r="201" spans="1:3">
       <c r="A201" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>88</v>
@@ -3884,10 +3875,10 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>88</v>
@@ -3895,10 +3886,10 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>88</v>
@@ -3906,10 +3897,10 @@
     </row>
     <row r="204" spans="1:3">
       <c r="A204" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>88</v>
@@ -3917,21 +3908,21 @@
     </row>
     <row r="205" spans="1:3">
       <c r="A205" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="7" t="s">
-        <v>306</v>
+      <c r="A206" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>88</v>
@@ -3939,139 +3930,139 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A208" s="1"/>
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>388</v>
+      <c r="A209" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="1"/>
-      <c r="B210" s="2"/>
-      <c r="C210" s="2"/>
+      <c r="A210" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="B212" s="9" t="s">
-        <v>318</v>
+        <v>308</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>317</v>
+        <v>309</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>318</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>320</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="217" spans="1:3">
-      <c r="A217" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>316</v>
-      </c>
+      <c r="A217" s="1"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>316</v>
-      </c>
+      <c r="A218" s="1"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="1"/>
-      <c r="B219" s="2"/>
-      <c r="C219" s="2"/>
+      <c r="A219" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="220" spans="1:3">
-      <c r="A220" s="1"/>
-      <c r="B220" s="2"/>
-      <c r="C220" s="2"/>
+      <c r="A220" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="1" t="s">
@@ -4097,10 +4088,10 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B223" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>88</v>
@@ -4108,10 +4099,10 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>88</v>
@@ -4119,10 +4110,10 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>88</v>
@@ -4130,10 +4121,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>88</v>
@@ -4141,10 +4132,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>88</v>
@@ -4152,10 +4143,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>88</v>
@@ -4163,10 +4154,10 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>88</v>
@@ -4174,10 +4165,10 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="1" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>88</v>
@@ -4185,10 +4176,10 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>88</v>
@@ -4196,25 +4187,19 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="1" t="s">
-        <v>384</v>
+        <v>297</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="233" spans="1:3">
-      <c r="A233" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A233" s="1"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" s="1"/>
@@ -4222,18 +4207,30 @@
       <c r="C234" s="2"/>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="1"/>
-      <c r="B235" s="2"/>
-      <c r="C235" s="2"/>
+      <c r="A235" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="236" spans="1:3">
-      <c r="A236" s="1"/>
-      <c r="B236" s="2"/>
-      <c r="C236" s="2"/>
+      <c r="A236" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="1" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>341</v>
@@ -4244,7 +4241,7 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>343</v>
@@ -4255,10 +4252,10 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>2</v>
@@ -4266,10 +4263,10 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>2</v>
@@ -4277,10 +4274,10 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>2</v>
@@ -4288,10 +4285,10 @@
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>2</v>
@@ -4299,10 +4296,10 @@
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>2</v>
@@ -4310,10 +4307,10 @@
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>2</v>
@@ -4321,10 +4318,10 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>2</v>
@@ -4332,7 +4329,7 @@
     </row>
     <row r="246" spans="1:3">
       <c r="A246" s="1" t="s">
-        <v>379</v>
+        <v>287</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>382</v>
@@ -4342,15 +4339,30 @@
       </c>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A247" s="1"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="1"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="1"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachanon.K\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachanon.K\Desktop\change model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9CE831-7DAE-44A4-B04D-0FDCF7C164FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4BE25B-13E4-4975-839A-9416C86B6956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="403">
   <si>
     <t>EFAZZ0001847</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -1194,14 +1194,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>800G PSM8    #10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>800G PSM8    #11</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>800G DR8 AWS #01</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
@@ -1463,6 +1455,9 @@
   </si>
   <si>
     <t>1.6T  DR8   NPI</t>
+  </si>
+  <si>
+    <t>800G PSM8    #01</t>
   </si>
 </sst>
 </file>
@@ -2648,10 +2643,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>88</v>
@@ -2662,7 +2657,7 @@
         <v>304</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>88</v>
@@ -2782,7 +2777,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>2</v>
@@ -2793,7 +2788,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>2</v>
@@ -2801,10 +2796,10 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>2</v>
@@ -2812,10 +2807,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>2</v>
@@ -2932,10 +2927,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>88</v>
@@ -2943,10 +2938,10 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>88</v>
@@ -3239,10 +3234,10 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>88</v>
@@ -3299,10 +3294,10 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>239</v>
@@ -3310,10 +3305,10 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>239</v>
@@ -3321,10 +3316,10 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>239</v>
@@ -3433,7 +3428,7 @@
         <v>147</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>88</v>
@@ -3444,7 +3439,7 @@
         <v>146</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>88</v>
@@ -3452,10 +3447,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>88</v>
@@ -3463,10 +3458,10 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>88</v>
@@ -3528,10 +3523,10 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>258</v>
@@ -3539,10 +3534,10 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>258</v>
@@ -3647,7 +3642,7 @@
         <v>274</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>2</v>
@@ -3679,7 +3674,7 @@
         <v>141</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>88</v>
@@ -3808,7 +3803,7 @@
         <v>9</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>2</v>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>2</v>
@@ -3922,7 +3917,7 @@
         <v>131</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>323</v>
+        <v>402</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>88</v>
@@ -3933,7 +3928,7 @@
         <v>132</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>88</v>
@@ -4044,10 +4039,10 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>88</v>
@@ -4055,10 +4050,10 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>88</v>
@@ -4066,10 +4061,10 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>88</v>
@@ -4077,10 +4072,10 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>88</v>
@@ -4088,10 +4083,10 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>88</v>
@@ -4099,10 +4094,10 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>88</v>
@@ -4110,10 +4105,10 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>88</v>
@@ -4121,10 +4116,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>88</v>
@@ -4132,10 +4127,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>88</v>
@@ -4143,10 +4138,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>88</v>
@@ -4154,10 +4149,10 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>88</v>
@@ -4165,10 +4160,10 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>88</v>
@@ -4176,10 +4171,10 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>88</v>
@@ -4190,7 +4185,7 @@
         <v>297</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>88</v>
@@ -4208,10 +4203,10 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>2</v>
@@ -4219,10 +4214,10 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>2</v>
@@ -4230,10 +4225,10 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>2</v>
@@ -4241,10 +4236,10 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>2</v>
@@ -4252,10 +4247,10 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>2</v>
@@ -4263,10 +4258,10 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>2</v>
@@ -4274,10 +4269,10 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>2</v>
@@ -4285,10 +4280,10 @@
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>2</v>
@@ -4296,10 +4291,10 @@
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>2</v>
@@ -4307,10 +4302,10 @@
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>2</v>
@@ -4318,10 +4313,10 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>2</v>
@@ -4332,7 +4327,7 @@
         <v>287</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>2</v>
@@ -4350,10 +4345,10 @@
     </row>
     <row r="249" spans="1:3">
       <c r="A249" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>2</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachanon.K\Desktop\change model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanchai.p\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4BE25B-13E4-4975-839A-9416C86B6956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9AB9EE-09F1-435F-B6A7-5D014738EFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="405">
   <si>
     <t>EFAZZ0001847</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -1034,21 +1034,6 @@
   </si>
   <si>
     <t>EFAZZ2400191</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>EQPTZ2500007</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>800G DR8  AWS   #03</t>
-  </si>
-  <si>
-    <t>EFAZZ0001703</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>200G BSM8   #01</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
@@ -1342,10 +1327,6 @@
     <t>EQPTZ2501105</t>
   </si>
   <si>
-    <t>400G PSM4   #15</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>EZDYH0000121</t>
   </si>
   <si>
@@ -1436,9 +1417,6 @@
     <t>EQPTZ2501093</t>
   </si>
   <si>
-    <t>800G 2XFR4    #09</t>
-  </si>
-  <si>
     <t>EZDYH2400195</t>
   </si>
   <si>
@@ -1458,6 +1436,30 @@
   </si>
   <si>
     <t>800G PSM8    #01</t>
+  </si>
+  <si>
+    <t>EQPTZ2500007</t>
+  </si>
+  <si>
+    <t>4X200G  DR4  GEN1</t>
+  </si>
+  <si>
+    <t>TXAA  NPI</t>
+  </si>
+  <si>
+    <t>EFAZZ0001703</t>
+  </si>
+  <si>
+    <t>400G  Q112  DR4</t>
+  </si>
+  <si>
+    <t>TRX FA   NPI</t>
+  </si>
+  <si>
+    <t>800G  2XFR4    #06</t>
+  </si>
+  <si>
+    <t>800G  2XFR4    #09</t>
   </si>
 </sst>
 </file>
@@ -1859,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C250"/>
+  <dimension ref="A1:C255"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.08984375" customWidth="1"/>
@@ -1891,7 +1893,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -2643,10 +2645,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>88</v>
@@ -2654,10 +2656,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>88</v>
@@ -2678,7 +2680,7 @@
         <v>273</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>2</v>
@@ -2766,7 +2768,7 @@
         <v>234</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>239</v>
@@ -2777,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>2</v>
@@ -2788,7 +2790,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>2</v>
@@ -2796,25 +2798,19 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A89" s="1"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="1"/>
@@ -2822,16 +2818,22 @@
       <c r="C90" s="2"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="1"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
+      <c r="A91" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>88</v>
@@ -2839,10 +2841,10 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>88</v>
@@ -2850,10 +2852,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>88</v>
@@ -2861,10 +2863,10 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>88</v>
@@ -2872,10 +2874,10 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>88</v>
@@ -2883,10 +2885,10 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>88</v>
@@ -2894,10 +2896,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>88</v>
@@ -2905,10 +2907,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>88</v>
@@ -2916,10 +2918,10 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="1" t="s">
-        <v>178</v>
+        <v>340</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>179</v>
+        <v>341</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>88</v>
@@ -2927,25 +2929,19 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A102" s="1"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="1"/>
@@ -3189,22 +3185,16 @@
       <c r="C125" s="2"/>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A126" s="1"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>88</v>
@@ -3212,10 +3202,10 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>88</v>
@@ -3223,10 +3213,10 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>88</v>
@@ -3234,48 +3224,42 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
-        <v>348</v>
+        <v>228</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>349</v>
+        <v>229</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131" s="1"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
+      <c r="A131" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>239</v>
-      </c>
+      <c r="A132" s="1"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>239</v>
-      </c>
+      <c r="A133" s="1"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>239</v>
@@ -3283,10 +3267,10 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>239</v>
@@ -3294,10 +3278,10 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="1" t="s">
-        <v>329</v>
+        <v>237</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>328</v>
+        <v>238</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>239</v>
@@ -3305,10 +3289,10 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="1" t="s">
-        <v>385</v>
+        <v>235</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>386</v>
+        <v>236</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>239</v>
@@ -3316,75 +3300,75 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="1" t="s">
-        <v>387</v>
+        <v>325</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139" s="1"/>
-      <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
+      <c r="A139" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="1"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
+      <c r="A140" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="1" t="s">
-        <v>240</v>
+        <v>359</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>241</v>
+        <v>403</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>88</v>
+        <v>239</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
-        <v>242</v>
+        <v>389</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>243</v>
+        <v>404</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>88</v>
+        <v>239</v>
       </c>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A143" s="1"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A144" s="1"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>88</v>
@@ -3392,10 +3376,10 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>88</v>
@@ -3403,10 +3387,10 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="1" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>88</v>
@@ -3414,10 +3398,10 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>88</v>
@@ -3425,10 +3409,10 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="1" t="s">
-        <v>147</v>
+        <v>248</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>325</v>
+        <v>249</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>88</v>
@@ -3436,10 +3420,10 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
-        <v>146</v>
+        <v>250</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>327</v>
+        <v>251</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>88</v>
@@ -3447,10 +3431,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="1" t="s">
-        <v>392</v>
+        <v>252</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>393</v>
+        <v>253</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>88</v>
@@ -3458,64 +3442,64 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="1" t="s">
-        <v>394</v>
+        <v>254</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>395</v>
+        <v>255</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="1"/>
-      <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
+      <c r="A153" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="1"/>
-      <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
+      <c r="A154" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="1" t="s">
-        <v>256</v>
+        <v>387</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>257</v>
+        <v>388</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>258</v>
+        <v>88</v>
       </c>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>258</v>
-      </c>
+      <c r="A156" s="1"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>258</v>
-      </c>
+      <c r="A157" s="1"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>258</v>
@@ -3523,10 +3507,10 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="1" t="s">
-        <v>389</v>
+        <v>259</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>390</v>
+        <v>260</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>258</v>
@@ -3534,46 +3518,52 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="1" t="s">
-        <v>396</v>
+        <v>261</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="1"/>
-      <c r="B161" s="2"/>
-      <c r="C161" s="2"/>
+      <c r="A161" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="1"/>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
+      <c r="A162" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="1" t="s">
-        <v>265</v>
+        <v>390</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>266</v>
+        <v>391</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>88</v>
+        <v>258</v>
       </c>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A164" s="1"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="1"/>
@@ -3581,19 +3571,25 @@
       <c r="C165" s="2"/>
     </row>
     <row r="166" spans="1:3">
-      <c r="A166" s="1"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="2"/>
+      <c r="A166" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>239</v>
+        <v>88</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -3608,13 +3604,13 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -3628,25 +3624,25 @@
       <c r="C172" s="2"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="1"/>
-      <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
+      <c r="A173" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1"/>
-      <c r="B174" s="4"/>
+      <c r="B174" s="2"/>
       <c r="C174" s="2"/>
     </row>
     <row r="175" spans="1:3">
-      <c r="A175" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A175" s="1"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="1"/>
@@ -3655,30 +3651,24 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="1"/>
-      <c r="B177" s="2"/>
+      <c r="B177" s="4"/>
       <c r="C177" s="2"/>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:3">
-      <c r="A179" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A179" s="1"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="1"/>
@@ -3686,20 +3676,20 @@
       <c r="C180" s="2"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="1"/>
-      <c r="B181" s="2"/>
-      <c r="C181" s="2"/>
+      <c r="A181" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="182" spans="1:3">
-      <c r="A182" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A182" s="1"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="1"/>
@@ -3712,21 +3702,33 @@
       <c r="C184" s="2"/>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="1"/>
-      <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
+      <c r="A185" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="1"/>
-      <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
+      <c r="A186" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>2</v>
@@ -3734,10 +3736,10 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>2</v>
@@ -3745,10 +3747,10 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>2</v>
@@ -3756,10 +3758,10 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>2</v>
@@ -3767,58 +3769,46 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:3">
-      <c r="A192" s="7" t="s">
-        <v>285</v>
+      <c r="A192" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="7" t="s">
-        <v>286</v>
+      <c r="A193" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>294</v>
+        <v>379</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A194" s="1"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A195" s="1"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" s="1"/>
@@ -3826,21 +3816,33 @@
       <c r="C196" s="2"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="1"/>
-      <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
+      <c r="A197" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="1"/>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
+      <c r="A198" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>88</v>
@@ -3848,10 +3850,10 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>88</v>
@@ -3859,10 +3861,10 @@
     </row>
     <row r="201" spans="1:3">
       <c r="A201" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>88</v>
@@ -3870,10 +3872,10 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>88</v>
@@ -3881,151 +3883,139 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" s="1"/>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" s="1"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="B203" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" s="1"/>
-      <c r="B208" s="2"/>
-      <c r="C208" s="2"/>
+      <c r="B208" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>314</v>
+        <v>304</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>312</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C213" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C213" s="4" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" s="8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>313</v>
-      </c>
+      <c r="A216" s="1"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" s="1"/>
@@ -4033,16 +4023,22 @@
       <c r="C217" s="2"/>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="1"/>
-      <c r="B218" s="2"/>
-      <c r="C218" s="2"/>
+      <c r="A218" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>88</v>
@@ -4050,10 +4046,10 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>88</v>
@@ -4061,10 +4057,10 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>88</v>
@@ -4072,10 +4068,10 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>88</v>
@@ -4083,10 +4079,10 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>88</v>
@@ -4094,10 +4090,10 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>88</v>
@@ -4105,10 +4101,10 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>88</v>
@@ -4116,10 +4112,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>88</v>
@@ -4127,10 +4123,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>88</v>
@@ -4138,10 +4134,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>88</v>
@@ -4149,10 +4145,10 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="1" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>88</v>
@@ -4160,10 +4156,10 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>88</v>
@@ -4171,25 +4167,19 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="232" spans="1:3">
-      <c r="A232" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A232" s="1"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" s="1"/>
@@ -4197,16 +4187,22 @@
       <c r="C233" s="2"/>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="1"/>
-      <c r="B234" s="2"/>
-      <c r="C234" s="2"/>
+      <c r="A234" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" s="1" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>2</v>
@@ -4214,10 +4210,10 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>2</v>
@@ -4225,10 +4221,10 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>2</v>
@@ -4236,10 +4232,10 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>2</v>
@@ -4247,10 +4243,10 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>2</v>
@@ -4258,10 +4254,10 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>2</v>
@@ -4269,10 +4265,10 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>2</v>
@@ -4280,10 +4276,10 @@
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>2</v>
@@ -4291,10 +4287,10 @@
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>2</v>
@@ -4302,10 +4298,10 @@
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>2</v>
@@ -4313,25 +4309,19 @@
     </row>
     <row r="245" spans="1:3">
       <c r="A245" s="1" t="s">
-        <v>374</v>
+        <v>283</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A246" s="1"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" s="1"/>
@@ -4339,25 +4329,62 @@
       <c r="C247" s="2"/>
     </row>
     <row r="248" spans="1:3">
-      <c r="A248" s="1"/>
-      <c r="B248" s="2"/>
-      <c r="C248" s="2"/>
+      <c r="A248" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="249" spans="1:3">
-      <c r="A249" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A249" s="1"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" s="1"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="1"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" s="1"/>
+      <c r="B253" s="2"/>
+      <c r="C253" s="2"/>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" s="1"/>
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
